--- a/excel_templates/Delivery Note.xlsx
+++ b/excel_templates/Delivery Note.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15105" windowHeight="8070"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="送货单" sheetId="23" r:id="rId1"/>
@@ -32,7 +32,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
-    <t>{{customs declaration}}</t>
+    <t>{{customs_declaration}}</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -76,10 +76,10 @@
     <t>余姚市新建北路347号 博源贸易  卢经理 收 13305844865</t>
   </si>
   <si>
-    <t>{{Contract No.}}</t>
+    <t>{{Contract_No.}}</t>
   </si>
   <si>
-    <t>{{Bill of Lading Number}}</t>
+    <t>{{Bill_of_Lading_Number}}</t>
   </si>
   <si>
     <t>备    注</t>
@@ -2024,7 +2024,7 @@
       <c r="G31" s="53"/>
       <c r="H31" s="66">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>

--- a/excel_templates/Delivery Note.xlsx
+++ b/excel_templates/Delivery Note.xlsx
@@ -76,7 +76,7 @@
     <t>余姚市新建北路347号 博源贸易  卢经理 收 13305844865</t>
   </si>
   <si>
-    <t>{{Contract_No.}}</t>
+    <t>{{Contract_No}}</t>
   </si>
   <si>
     <t>{{Bill_of_Lading_Number}}</t>
@@ -2024,7 +2024,7 @@
       <c r="G31" s="53"/>
       <c r="H31" s="66">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>

--- a/excel_templates/Delivery Note.xlsx
+++ b/excel_templates/Delivery Note.xlsx
@@ -30,7 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+  <si>
+    <t>{{Proxy_client}}</t>
+  </si>
   <si>
     <t>{{customs_declaration}}</t>
   </si>
@@ -1445,9 +1448,8 @@
     <row r="3" ht="39" customHeight="1" spans="4:22">
       <c r="D3" s="9"/>
       <c r="E3" s="10"/>
-      <c r="F3" s="11" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="F3" s="11" t="s">
+        <v>0</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
@@ -1466,7 +1468,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="16"/>
       <c r="G4" s="6" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
@@ -1511,7 +1513,7 @@
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
       <c r="F7" s="24" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -1565,12 +1567,12 @@
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="R10" s="25" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1" spans="4:22">
       <c r="D11" s="26" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
@@ -1604,13 +1606,13 @@
       <c r="O12" s="29"/>
       <c r="P12" s="33"/>
       <c r="Q12" s="25" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R12" s="25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" s="25"/>
       <c r="U12" s="34"/>
@@ -1640,10 +1642,10 @@
         <v>1</v>
       </c>
       <c r="R13" s="38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S13" s="39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" s="39"/>
       <c r="U13" s="39"/>
@@ -1714,7 +1716,7 @@
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="43" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="43"/>
       <c r="H16" s="43"/>
@@ -1738,13 +1740,13 @@
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="4:22">
       <c r="D17" s="46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="46"/>
       <c r="F17" s="47"/>
       <c r="G17" s="47"/>
       <c r="H17" s="10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1790,7 +1792,7 @@
       <c r="M19" s="7"/>
       <c r="N19" s="50"/>
       <c r="O19" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P19" s="51"/>
       <c r="Q19" s="51"/>
@@ -1808,7 +1810,7 @@
       <c r="M20" s="7"/>
       <c r="N20" s="50"/>
       <c r="O20" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P20" s="52"/>
       <c r="Q20" s="52"/>
@@ -1819,7 +1821,7 @@
       <c r="F21" s="47"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
@@ -1867,10 +1869,10 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="22.5" customHeight="1" spans="4:22">
       <c r="D24" s="45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F24" s="57"/>
       <c r="G24" s="57"/>
@@ -1892,7 +1894,7 @@
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="4:22">
       <c r="D25" s="61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="62" t="str">
         <f>S13&amp;""</f>
@@ -2017,7 +2019,7 @@
     </row>
     <row r="31" ht="29.25" customHeight="1" spans="4:22">
       <c r="D31" s="53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" s="53"/>
       <c r="F31" s="53"/>
